--- a/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
@@ -1471,13 +1471,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 13:41:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:30</t>
+    <t>Fecha y hora de generación: 05/11/2025 13:41:32</t>
   </si>
 </sst>
 </file>

--- a/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
@@ -1471,13 +1471,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 12:35:17</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:30</t>
+    <t>Fecha y hora de generación: 04/11/2025 12:35:39</t>
   </si>
 </sst>
 </file>

--- a/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
+++ b/Macro Inv Tarde/VALORIZADO FALTANTES.xlsx
@@ -1471,13 +1471,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 13:41:04</t>
+    <t>Período: 30/11/2025 13:21:00</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 05/11/2025 13:41:32</t>
+    <t>Fecha y hora de generación: 06/11/2025 13:21:26</t>
   </si>
 </sst>
 </file>
